--- a/site/public/ig/all-profiles.xlsx
+++ b/site/public/ig/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9089" uniqueCount="1122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9292" uniqueCount="1132">
   <si>
     <t>Property</t>
   </si>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T20:13:50-04:00</t>
+    <t>2026-09-17T14:02:25-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2468,7 +2468,7 @@
     <t>HEARTLAND Remote Monitoring Observation</t>
   </si>
   <si>
-    <t>Observation captured via the HEARTLAND remote monitoring kit (Module 5): body weight, blood pressure (systolic/diastolic), or oxygen saturation. Red-flag thresholds are encoded via Observation.referenceRange with meaning.text identifying the rule. Default thresholds (HEARTLAND v3.2 standard, configurable per program): weight gain &gt;=2 lb (0.9 kg)/24h or &gt;=5 lb (2.3 kg)/7d; SBP &lt;90 or &gt;180 mmHg; DBP &lt;50 or &gt;110 mmHg; SpO2 &lt;90% on room air. Per the human filter principle, all non-emergency alerts pass through licensed clinician telephone assessment before ED referral.</t>
+    <t>Observation captured via the HEARTLAND remote monitoring kit (Module 5): body weight, blood pressure (systolic/diastolic), or oxygen saturation. Red-flag thresholds are encoded via Observation.referenceRange with meaning.text identifying the rule. The weight and oxygen saturation values a program configures here are starting defaults, not HEARTLAND Protocol rules: weight gain &gt;=2 lb (0.9 kg)/24h or &gt;=5 lb (2.3 kg)/7d, and SpO2 &lt;90% on room air, all configurable per program. Systolic BP &lt;90 mmHg is the only blood pressure red flag; this guide states no diastolic threshold and no high systolic threshold. Per the human filter principle, all non-emergency alerts pass through licensed clinician telephone assessment before ED referral.</t>
   </si>
   <si>
     <t>Observation</t>
@@ -3148,7 +3148,7 @@
     <t>HEARTLAND Risk Assessment</t>
   </si>
   <si>
-    <t>Heart failure risk stratification per the HEARTLAND Protocol v3.2 risk score. The score sums up to 18 points across 10 binary inputs and maps to three qualitative tiers: low (0-4), moderate (5-8), high (&gt;=9). The basis SHALL reference a HeartlandRiskInputQuestionnaire QuestionnaireResponse capturing the 10 input variables.</t>
+    <t>Heart failure risk stratification per the HEARTLAND Protocol v3.2 risk score. The score sums up to 18 points across 10 binary inputs and maps to three qualitative tiers: low (0-4), moderate (5-8), high (&gt;=9). It is a non-validated implementation heuristic that assigns monitoring intensity; it does not predict an outcome and has not been validated against outcome data. The basis SHALL reference a HeartlandRiskInputQuestionnaire QuestionnaireResponse capturing the 10 input variables, or an Observation carrying the point total. The tier travels in prediction.qualitativeRisk and the point total in the heartland-risk-score-total extension; probability[x] is prohibited, because a point count is not a likelihood of an outcome.</t>
   </si>
   <si>
     <t>RiskAssessment</t>
@@ -3402,6 +3402,22 @@
     <t>RiskAssessment.prediction.extension</t>
   </si>
   <si>
+    <t>RiskAssessment.prediction.extension:scoreTotal</t>
+  </si>
+  <si>
+    <t>scoreTotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://fhir.heartlandprotocol.org/StructureDefinition/heartland-risk-score-total}
+</t>
+  </si>
+  <si>
+    <t>Total HEARTLAND risk score (0-18 heuristic points, not a probability)</t>
+  </si>
+  <si>
+    <t>Total of the HEARTLAND risk score: an integer count of 0 to 18 points summed from ten binary inputs. This is a non-validated implementation heuristic used to assign monitoring intensity; it is a point total, not a probability, not a predicted event rate and not a validated prognostic estimate. It is carried in this extension rather than in RiskAssessment.prediction.probabilityDecimal because that element is defined in FHIR R4 as the likelihood of a specified outcome, expressed as a percentage.</t>
+  </si>
+  <si>
     <t>RiskAssessment.prediction.modifierExtension</t>
   </si>
   <si>
@@ -3437,15 +3453,6 @@
 ras-1:low and high must be percentages, if present {(low.empty() or ((low.code = '%') and (low.system = %ucum))) and (high.empty() or ((high.code = '%') and (high.system = %ucum)))}</t>
   </si>
   <si>
-    <t>RiskAssessment.prediction.probability[x]:probabilityDecimal</t>
-  </si>
-  <si>
-    <t>probabilityDecimal</t>
-  </si>
-  <si>
-    <t>Total HEARTLAND risk score (0-18 integer points)</t>
-  </si>
-  <si>
     <t>RiskAssessment.prediction.qualitativeRisk</t>
   </si>
   <si>
@@ -3514,6 +3521,31 @@
   </si>
   <si>
     <t>Additional comments about the risk assessment.</t>
+  </si>
+  <si>
+    <t>heartland-risk-score-total</t>
+  </si>
+  <si>
+    <t>https://fhir.heartlandprotocol.org/StructureDefinition/heartland-risk-score-total</t>
+  </si>
+  <si>
+    <t>HeartlandRiskScoreTotal</t>
+  </si>
+  <si>
+    <t>HEARTLAND Risk Score Total</t>
+  </si>
+  <si>
+    <t>element:RiskAssessment.prediction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">integer
+</t>
+  </si>
+  <si>
+    <t>HEARTLAND risk score point total (0-18), a heuristic count and not a probability</t>
+  </si>
+  <si>
+    <t>18</t>
   </si>
   <si>
     <t>heartland-social-support-score</t>
@@ -3656,7 +3688,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B204"/>
+  <dimension ref="A1:B227"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -5092,7 +5124,7 @@
         <v>2</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>1119</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="184">
@@ -5100,7 +5132,7 @@
         <v>4</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>1120</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="185">
@@ -5116,7 +5148,7 @@
         <v>8</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>1121</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="187">
@@ -5124,7 +5156,7 @@
         <v>10</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>503</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="188">
@@ -5188,7 +5220,7 @@
         <v>25</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>504</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="196">
@@ -5256,6 +5288,186 @@
         <v>419</v>
       </c>
       <c r="B204" t="s" s="2">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B205" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="B206" t="s" s="2">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="B207" t="s" s="2">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="B208" t="s" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s" s="2">
+        <v>8</v>
+      </c>
+      <c r="B209" t="s" s="2">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s" s="2">
+        <v>10</v>
+      </c>
+      <c r="B210" t="s" s="2">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="B211" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B212" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="B213" t="s" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="B214" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B215" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B216" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="B217" t="s" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B218" t="s" s="2">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B219" s="2"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B220" s="2"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B221" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B222" t="s" s="2">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B223" t="s" s="2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B224" t="s" s="2">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B225" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B226" t="s" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="B227" t="s" s="2">
         <v>420</v>
       </c>
     </row>
@@ -5266,11 +5478,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK262"/>
+  <dimension ref="A1:AK267"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="34.9140625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="49.24609375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="45.6640625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="45.6640625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="18.18359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="41.75390625" customWidth="true" bestFit="true"/>
@@ -31200,7 +31412,7 @@
       </c>
       <c r="D247" s="2"/>
       <c r="E247" t="s" s="2">
-        <v>147</v>
+        <v>79</v>
       </c>
       <c r="F247" s="2"/>
       <c r="G247" t="s" s="2">
@@ -31222,14 +31434,12 @@
         <v>128</v>
       </c>
       <c r="M247" t="s" s="2">
-        <v>279</v>
+        <v>129</v>
       </c>
       <c r="N247" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O247" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="O247" s="2"/>
       <c r="P247" s="2"/>
       <c r="Q247" t="s" s="2">
         <v>79</v>
@@ -31266,16 +31476,14 @@
         <v>79</v>
       </c>
       <c r="AC247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD247" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="AD247" s="2"/>
       <c r="AE247" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AF247" t="s" s="2">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="AG247" t="s" s="2">
         <v>281</v>
@@ -31301,43 +31509,41 @@
         <v>1082</v>
       </c>
       <c r="C248" t="s" s="2">
-        <v>1082</v>
-      </c>
-      <c r="D248" s="2"/>
+        <v>1081</v>
+      </c>
+      <c r="D248" t="s" s="2">
+        <v>1083</v>
+      </c>
       <c r="E248" t="s" s="2">
-        <v>283</v>
+        <v>79</v>
       </c>
       <c r="F248" s="2"/>
       <c r="G248" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H248" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I248" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="J248" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="K248" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="L248" t="s" s="2">
-        <v>128</v>
+        <v>1084</v>
       </c>
       <c r="M248" t="s" s="2">
-        <v>284</v>
+        <v>1085</v>
       </c>
       <c r="N248" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O248" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="P248" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>1086</v>
+      </c>
+      <c r="O248" s="2"/>
+      <c r="P248" s="2"/>
       <c r="Q248" t="s" s="2">
         <v>79</v>
       </c>
@@ -31385,7 +31591,7 @@
         <v>79</v>
       </c>
       <c r="AG248" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="AH248" t="s" s="2">
         <v>77</v>
@@ -31394,7 +31600,7 @@
         <v>78</v>
       </c>
       <c r="AJ248" t="s" s="2">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="AK248" t="s" s="2">
         <v>134</v>
@@ -31405,42 +31611,46 @@
         <v>995</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="C249" t="s" s="2">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="D249" s="2"/>
       <c r="E249" t="s" s="2">
-        <v>79</v>
+        <v>283</v>
       </c>
       <c r="F249" s="2"/>
       <c r="G249" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H249" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I249" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J249" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="K249" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="L249" t="s" s="2">
-        <v>198</v>
+        <v>128</v>
       </c>
       <c r="M249" t="s" s="2">
-        <v>1084</v>
+        <v>284</v>
       </c>
       <c r="N249" t="s" s="2">
-        <v>1085</v>
-      </c>
-      <c r="O249" s="2"/>
-      <c r="P249" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="O249" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="P249" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="Q249" t="s" s="2">
         <v>79</v>
       </c>
@@ -31464,10 +31674,10 @@
         <v>79</v>
       </c>
       <c r="Y249" t="s" s="2">
-        <v>203</v>
+        <v>79</v>
       </c>
       <c r="Z249" t="s" s="2">
-        <v>1086</v>
+        <v>79</v>
       </c>
       <c r="AA249" t="s" s="2">
         <v>79</v>
@@ -31488,19 +31698,19 @@
         <v>79</v>
       </c>
       <c r="AG249" t="s" s="2">
-        <v>1083</v>
+        <v>286</v>
       </c>
       <c r="AH249" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI249" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AJ249" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AK249" t="s" s="2">
-        <v>97</v>
+        <v>134</v>
       </c>
     </row>
     <row r="250">
@@ -31508,10 +31718,10 @@
         <v>995</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="C250" t="s" s="2">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="D250" s="2"/>
       <c r="E250" t="s" s="2">
@@ -31534,7 +31744,7 @@
         <v>79</v>
       </c>
       <c r="L250" t="s" s="2">
-        <v>1088</v>
+        <v>198</v>
       </c>
       <c r="M250" t="s" s="2">
         <v>1089</v>
@@ -31542,9 +31752,7 @@
       <c r="N250" t="s" s="2">
         <v>1090</v>
       </c>
-      <c r="O250" t="s" s="2">
-        <v>1091</v>
-      </c>
+      <c r="O250" s="2"/>
       <c r="P250" s="2"/>
       <c r="Q250" t="s" s="2">
         <v>79</v>
@@ -31569,10 +31777,10 @@
         <v>79</v>
       </c>
       <c r="Y250" t="s" s="2">
-        <v>79</v>
+        <v>203</v>
       </c>
       <c r="Z250" t="s" s="2">
-        <v>79</v>
+        <v>1091</v>
       </c>
       <c r="AA250" t="s" s="2">
         <v>79</v>
@@ -31581,17 +31789,19 @@
         <v>79</v>
       </c>
       <c r="AC250" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="AD250" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AD250" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AE250" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AF250" t="s" s="2">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="AG250" t="s" s="2">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="AH250" t="s" s="2">
         <v>77</v>
@@ -31603,7 +31813,7 @@
         <v>79</v>
       </c>
       <c r="AK250" t="s" s="2">
-        <v>1092</v>
+        <v>97</v>
       </c>
     </row>
     <row r="251">
@@ -31611,14 +31821,12 @@
         <v>995</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C251" t="s" s="2">
-        <v>1087</v>
-      </c>
-      <c r="D251" t="s" s="2">
-        <v>1094</v>
-      </c>
+        <v>1092</v>
+      </c>
+      <c r="D251" s="2"/>
       <c r="E251" t="s" s="2">
         <v>79</v>
       </c>
@@ -31627,7 +31835,7 @@
         <v>77</v>
       </c>
       <c r="H251" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I251" t="s" s="2">
         <v>79</v>
@@ -31639,16 +31847,16 @@
         <v>79</v>
       </c>
       <c r="L251" t="s" s="2">
-        <v>435</v>
+        <v>1093</v>
       </c>
       <c r="M251" t="s" s="2">
+        <v>1094</v>
+      </c>
+      <c r="N251" t="s" s="2">
         <v>1095</v>
       </c>
-      <c r="N251" t="s" s="2">
-        <v>1090</v>
-      </c>
       <c r="O251" t="s" s="2">
-        <v>1091</v>
+        <v>1096</v>
       </c>
       <c r="P251" s="2"/>
       <c r="Q251" t="s" s="2">
@@ -31698,7 +31906,7 @@
         <v>79</v>
       </c>
       <c r="AG251" t="s" s="2">
-        <v>1087</v>
+        <v>1092</v>
       </c>
       <c r="AH251" t="s" s="2">
         <v>77</v>
@@ -31710,7 +31918,7 @@
         <v>79</v>
       </c>
       <c r="AK251" t="s" s="2">
-        <v>1092</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="252">
@@ -31718,10 +31926,10 @@
         <v>995</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="C252" t="s" s="2">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="D252" s="2"/>
       <c r="E252" t="s" s="2">
@@ -31747,10 +31955,10 @@
         <v>198</v>
       </c>
       <c r="M252" t="s" s="2">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="N252" t="s" s="2">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="O252" s="2"/>
       <c r="P252" s="2"/>
@@ -31781,7 +31989,7 @@
       </c>
       <c r="Z252" s="2"/>
       <c r="AA252" t="s" s="2">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="AB252" t="s" s="2">
         <v>79</v>
@@ -31799,7 +32007,7 @@
         <v>79</v>
       </c>
       <c r="AG252" t="s" s="2">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="AH252" t="s" s="2">
         <v>77</v>
@@ -31819,10 +32027,10 @@
         <v>995</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="C253" t="s" s="2">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="D253" s="2"/>
       <c r="E253" t="s" s="2">
@@ -31848,14 +32056,14 @@
         <v>435</v>
       </c>
       <c r="M253" t="s" s="2">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="N253" t="s" s="2">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="O253" s="2"/>
       <c r="P253" t="s" s="2">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="Q253" t="s" s="2">
         <v>79</v>
@@ -31904,7 +32112,7 @@
         <v>79</v>
       </c>
       <c r="AG253" t="s" s="2">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="AH253" t="s" s="2">
         <v>77</v>
@@ -31924,10 +32132,10 @@
         <v>995</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="C254" t="s" s="2">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="D254" s="2"/>
       <c r="E254" t="s" s="2">
@@ -31950,16 +32158,16 @@
         <v>79</v>
       </c>
       <c r="L254" t="s" s="2">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="M254" t="s" s="2">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="N254" t="s" s="2">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="O254" t="s" s="2">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="P254" s="2"/>
       <c r="Q254" t="s" s="2">
@@ -32009,7 +32217,7 @@
         <v>79</v>
       </c>
       <c r="AG254" t="s" s="2">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="AH254" t="s" s="2">
         <v>77</v>
@@ -32029,10 +32237,10 @@
         <v>995</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="C255" t="s" s="2">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="D255" s="2"/>
       <c r="E255" t="s" s="2">
@@ -32058,10 +32266,10 @@
         <v>207</v>
       </c>
       <c r="M255" t="s" s="2">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="N255" t="s" s="2">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="O255" s="2"/>
       <c r="P255" s="2"/>
@@ -32112,7 +32320,7 @@
         <v>79</v>
       </c>
       <c r="AG255" t="s" s="2">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="AH255" t="s" s="2">
         <v>77</v>
@@ -32132,10 +32340,10 @@
         <v>995</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="C256" t="s" s="2">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="D256" s="2"/>
       <c r="E256" t="s" s="2">
@@ -32161,14 +32369,14 @@
         <v>207</v>
       </c>
       <c r="M256" t="s" s="2">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="N256" t="s" s="2">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="O256" s="2"/>
       <c r="P256" t="s" s="2">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="Q256" t="s" s="2">
         <v>79</v>
@@ -32217,7 +32425,7 @@
         <v>79</v>
       </c>
       <c r="AG256" t="s" s="2">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="AH256" t="s" s="2">
         <v>77</v>
@@ -32237,10 +32445,10 @@
         <v>995</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="C257" t="s" s="2">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="D257" s="2"/>
       <c r="E257" t="s" s="2">
@@ -32266,10 +32474,10 @@
         <v>299</v>
       </c>
       <c r="M257" t="s" s="2">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="N257" t="s" s="2">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="O257" s="2"/>
       <c r="P257" s="2"/>
@@ -32320,7 +32528,7 @@
         <v>79</v>
       </c>
       <c r="AG257" t="s" s="2">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="AH257" t="s" s="2">
         <v>77</v>
@@ -32337,7 +32545,7 @@
     </row>
     <row r="258">
       <c r="A258" t="s" s="2">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="B258" t="s" s="2">
         <v>129</v>
@@ -32369,10 +32577,10 @@
         <v>80</v>
       </c>
       <c r="M258" t="s" s="2">
-        <v>503</v>
+        <v>1124</v>
       </c>
       <c r="N258" t="s" s="2">
-        <v>504</v>
+        <v>1086</v>
       </c>
       <c r="O258" s="2"/>
       <c r="P258" s="2"/>
@@ -32440,7 +32648,7 @@
     </row>
     <row r="259">
       <c r="A259" t="s" s="2">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="B259" t="s" s="2">
         <v>421</v>
@@ -32543,7 +32751,7 @@
     </row>
     <row r="260">
       <c r="A260" t="s" s="2">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="B260" t="s" s="2">
         <v>422</v>
@@ -32646,7 +32854,7 @@
     </row>
     <row r="261">
       <c r="A261" t="s" s="2">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="B261" t="s" s="2">
         <v>424</v>
@@ -32692,7 +32900,7 @@
       </c>
       <c r="R261" s="2"/>
       <c r="S261" t="s" s="2">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="T261" t="s" s="2">
         <v>79</v>
@@ -32751,7 +32959,7 @@
     </row>
     <row r="262">
       <c r="A262" t="s" s="2">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="B262" t="s" s="2">
         <v>428</v>
@@ -32780,10 +32988,10 @@
         <v>79</v>
       </c>
       <c r="L262" t="s" s="2">
-        <v>364</v>
+        <v>1126</v>
       </c>
       <c r="M262" t="s" s="2">
-        <v>430</v>
+        <v>1127</v>
       </c>
       <c r="N262" t="s" s="2">
         <v>431</v>
@@ -32804,10 +33012,10 @@
         <v>79</v>
       </c>
       <c r="V262" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="W262" t="s" s="2">
-        <v>79</v>
+        <v>1128</v>
       </c>
       <c r="X262" t="s" s="2">
         <v>79</v>
@@ -32849,6 +33057,523 @@
         <v>79</v>
       </c>
       <c r="AK262" t="s" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="s" s="2">
+        <v>1129</v>
+      </c>
+      <c r="B263" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="C263" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="D263" s="2"/>
+      <c r="E263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="F263" s="2"/>
+      <c r="G263" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H263" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L263" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="M263" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="N263" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="O263" s="2"/>
+      <c r="P263" s="2"/>
+      <c r="Q263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="R263" s="2"/>
+      <c r="S263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG263" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="AH263" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI263" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ263" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK263" t="s" s="2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="s" s="2">
+        <v>1129</v>
+      </c>
+      <c r="B264" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="C264" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="D264" s="2"/>
+      <c r="E264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="F264" s="2"/>
+      <c r="G264" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H264" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L264" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M264" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="N264" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="O264" s="2"/>
+      <c r="P264" s="2"/>
+      <c r="Q264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="R264" s="2"/>
+      <c r="S264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG264" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AH264" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI264" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK264" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="s" s="2">
+        <v>1129</v>
+      </c>
+      <c r="B265" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="C265" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="D265" s="2"/>
+      <c r="E265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="F265" s="2"/>
+      <c r="G265" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H265" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L265" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M265" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="N265" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="O265" s="2"/>
+      <c r="P265" s="2"/>
+      <c r="Q265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="R265" s="2"/>
+      <c r="S265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC265" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AD265" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AE265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF265" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AG265" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AH265" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI265" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK265" t="s" s="2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="s" s="2">
+        <v>1129</v>
+      </c>
+      <c r="B266" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="C266" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="D266" s="2"/>
+      <c r="E266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="F266" s="2"/>
+      <c r="G266" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H266" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L266" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M266" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="N266" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="O266" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="P266" s="2"/>
+      <c r="Q266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="R266" s="2"/>
+      <c r="S266" t="s" s="2">
+        <v>1130</v>
+      </c>
+      <c r="T266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG266" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AH266" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI266" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK266" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="s" s="2">
+        <v>1129</v>
+      </c>
+      <c r="B267" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="C267" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="D267" s="2"/>
+      <c r="E267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="F267" s="2"/>
+      <c r="G267" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H267" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L267" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M267" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="N267" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="O267" s="2"/>
+      <c r="P267" s="2"/>
+      <c r="Q267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="R267" s="2"/>
+      <c r="S267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG267" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AH267" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI267" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK267" t="s" s="2">
         <v>97</v>
       </c>
     </row>

--- a/site/public/ig/all-profiles.xlsx
+++ b/site/public/ig/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T14:02:25-04:00</t>
+    <t>2026-09-17T14:11:14-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
